--- a/automotive_forms/015_vehicle_interior_assessment_survey--automotive_forms.xlsx
+++ b/automotive_forms/015_vehicle_interior_assessment_survey--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1263,8 +1263,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'newer_than_10',_'value':_'newer_than_10'}</t>
+          <t>newer_than_10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Newer than 10', 'value': 'Newer than 10'}</t>
+          <t>Newer than 10</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'10-20',_'value':_'10-20'}</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': '10-20', 'value': '10-20'}</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'21-30',_'value':_'21-30'}</t>
+          <t>21-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': '21-30', 'value': '21-30'}</t>
+          <t>21-30</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'31-40',_'value':_'31-40'}</t>
+          <t>31-40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': '31-40', 'value': '31-40'}</t>
+          <t>31-40</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'older_than_40',_'value':_'older_than_40'}</t>
+          <t>older_than_40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Older than 40', 'value': 'Older than 40'}</t>
+          <t>Older than 40</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'black',_'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Black', 'value': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'blue',_'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Blue', 'value': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'white',_'value':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'White', 'value': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'red',_'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Red', 'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
